--- a/Catalogue-icones.xlsx
+++ b/Catalogue-icones.xlsx
@@ -430,7 +430,7 @@
     <x:row r="6" ht="34" customHeight="1">
       <x:c r="A6" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3dicons-video-camera-front-color-1.svg</x:t>
+          <x:t xml:space="preserve">Eclairage_Device_Off.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="8" t="inlineStr">
@@ -440,16 +440,16 @@
       </x:c>
       <x:c r="C6" s="9" t="str">
         <x:f>IF(A6="","",IFERROR(IF(VLOOKUP(B6,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B6,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D6" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3dicons-video-camera-front-color-1</x:t>
+          <x:t xml:space="preserve">Eclairage Device Off</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" s="9" t="str">
         <x:f>IF(A6="","",LOWER(B6&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A6),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-3dicons-video-camera-front-color-1</x:v>
+        <x:v>lib001-eclairage_device_off</x:v>
       </x:c>
       <x:c r="F6" s="8" t="inlineStr">
         <x:is>
@@ -463,7 +463,7 @@
       </x:c>
       <x:c r="H6" s="10" t="str">
         <x:f>IF(A6="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A6," ","%20"))</x:f>
-        <x:v>3dicons-video-camera-front-color-1.svg</x:v>
+        <x:v>Eclairage_Device_Off.svg</x:v>
       </x:c>
       <x:c r="I6" s="8" t="inlineStr">
         <x:is>
@@ -479,7 +479,7 @@
     <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3dicons-video-camera-front-color.svg</x:t>
+          <x:t xml:space="preserve">Moteur_Device_Store.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" s="8" t="inlineStr">
@@ -489,16 +489,16 @@
       </x:c>
       <x:c r="C7" s="9" t="str">
         <x:f>IF(A7="","",IFERROR(IF(VLOOKUP(B7,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B7,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D7" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3dicons-video-camera-front-color</x:t>
+          <x:t xml:space="preserve">Moteur Device Store</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" s="9" t="str">
         <x:f>IF(A7="","",LOWER(B7&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A7),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-3dicons-video-camera-front-color</x:v>
+        <x:v>lib001-moteur_device_store</x:v>
       </x:c>
       <x:c r="F7" s="8" t="inlineStr">
         <x:is>
@@ -512,7 +512,7 @@
       </x:c>
       <x:c r="H7" s="10" t="str">
         <x:f>IF(A7="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A7," ","%20"))</x:f>
-        <x:v>3dicons-video-camera-front-color.svg</x:v>
+        <x:v>Moteur_Device_Store.svg</x:v>
       </x:c>
       <x:c r="I7" s="8" t="inlineStr">
         <x:is>
@@ -528,7 +528,7 @@
     <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ampoule-1.svg</x:t>
+          <x:t xml:space="preserve">Navigation_Commande_Down.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="8" t="inlineStr">
@@ -538,30 +538,30 @@
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:f>IF(A8="","",IFERROR(IF(VLOOKUP(B8,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B8,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D8" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ampoule-1</x:t>
+          <x:t xml:space="preserve">Down</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" s="9" t="str">
         <x:f>IF(A8="","",LOWER(B8&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A8),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-ampoule-1</x:v>
+        <x:v>lib001-navigation_commande_down</x:v>
       </x:c>
       <x:c r="F8" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Navigation</x:t>
         </x:is>
       </x:c>
       <x:c r="G8" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" s="10" t="str">
         <x:f>IF(A8="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A8," ","%20"))</x:f>
-        <x:v>Ampoule-1.svg</x:v>
+        <x:v>Navigation_Commande_Down.svg</x:v>
       </x:c>
       <x:c r="I8" s="8" t="inlineStr">
         <x:is>
@@ -577,7 +577,7 @@
     <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ampoule.svg</x:t>
+          <x:t xml:space="preserve">Navigation_Commande_Left.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" s="8" t="inlineStr">
@@ -587,30 +587,30 @@
       </x:c>
       <x:c r="C9" s="9" t="str">
         <x:f>IF(A9="","",IFERROR(IF(VLOOKUP(B9,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B9,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D9" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Ampoule</x:t>
+          <x:t xml:space="preserve">Left</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" s="9" t="str">
         <x:f>IF(A9="","",LOWER(B9&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A9),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-ampoule</x:v>
+        <x:v>lib001-navigation_commande_left</x:v>
       </x:c>
       <x:c r="F9" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Navigation</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" s="10" t="str">
         <x:f>IF(A9="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A9," ","%20"))</x:f>
-        <x:v>Ampoule.svg</x:v>
+        <x:v>Navigation_Commande_Left.svg</x:v>
       </x:c>
       <x:c r="I9" s="8" t="inlineStr">
         <x:is>
@@ -626,7 +626,7 @@
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone HDMI-1.svg</x:t>
+          <x:t xml:space="preserve">Navigation_Commande_ONOFF.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" s="8" t="inlineStr">
@@ -636,30 +636,30 @@
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:f>IF(A10="","",IFERROR(IF(VLOOKUP(B10,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B10,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D10" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone HDMI-1</x:t>
+          <x:t xml:space="preserve">ONOFF</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" s="9" t="str">
         <x:f>IF(A10="","",LOWER(B10&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A10),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone-hdmi-1</x:v>
+        <x:v>lib001-navigation_commande_onoff</x:v>
       </x:c>
       <x:c r="F10" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Navigation</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" s="10" t="str">
         <x:f>IF(A10="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A10," ","%20"))</x:f>
-        <x:v>Icone%20HDMI-1.svg</x:v>
+        <x:v>Navigation_Commande_ONOFF.svg</x:v>
       </x:c>
       <x:c r="I10" s="8" t="inlineStr">
         <x:is>
@@ -675,7 +675,7 @@
     <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone HDMI.svg</x:t>
+          <x:t xml:space="preserve">Navigation_Commande_Retour.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="8" t="inlineStr">
@@ -685,30 +685,30 @@
       </x:c>
       <x:c r="C11" s="9" t="str">
         <x:f>IF(A11="","",IFERROR(IF(VLOOKUP(B11,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B11,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D11" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone HDMI</x:t>
+          <x:t xml:space="preserve">Retour</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" s="9" t="str">
         <x:f>IF(A11="","",LOWER(B11&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A11),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone-hdmi</x:v>
+        <x:v>lib001-navigation_commande_retour</x:v>
       </x:c>
       <x:c r="F11" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Navigation</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" s="10" t="str">
         <x:f>IF(A11="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A11," ","%20"))</x:f>
-        <x:v>Icone%20HDMI.svg</x:v>
+        <x:v>Navigation_Commande_Retour.svg</x:v>
       </x:c>
       <x:c r="I11" s="8" t="inlineStr">
         <x:is>
@@ -724,7 +724,7 @@
     <x:row r="12" ht="34" customHeight="1">
       <x:c r="A12" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_BYOD.svg</x:t>
+          <x:t xml:space="preserve">Navigation_Commande_Right.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" s="8" t="inlineStr">
@@ -734,30 +734,30 @@
       </x:c>
       <x:c r="C12" s="9" t="str">
         <x:f>IF(A12="","",IFERROR(IF(VLOOKUP(B12,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B12,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D12" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone BYOD</x:t>
+          <x:t xml:space="preserve">Right</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" s="9" t="str">
         <x:f>IF(A12="","",LOWER(B12&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A12),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_byod</x:v>
+        <x:v>lib001-navigation_commande_right</x:v>
       </x:c>
       <x:c r="F12" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Navigation</x:t>
         </x:is>
       </x:c>
       <x:c r="G12" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" s="10" t="str">
         <x:f>IF(A12="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A12," ","%20"))</x:f>
-        <x:v>Icone_BYOD.svg</x:v>
+        <x:v>Navigation_Commande_Right.svg</x:v>
       </x:c>
       <x:c r="I12" s="8" t="inlineStr">
         <x:is>
@@ -773,7 +773,7 @@
     <x:row r="13" ht="34" customHeight="1">
       <x:c r="A13" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_ClickShare-1.svg</x:t>
+          <x:t xml:space="preserve">Navigation_Commande_Up.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="8" t="inlineStr">
@@ -783,30 +783,30 @@
       </x:c>
       <x:c r="C13" s="9" t="str">
         <x:f>IF(A13="","",IFERROR(IF(VLOOKUP(B13,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B13,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D13" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone ClickShare-1</x:t>
+          <x:t xml:space="preserve">Up</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" s="9" t="str">
         <x:f>IF(A13="","",LOWER(B13&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A13),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_clickshare-1</x:v>
+        <x:v>lib001-navigation_commande_up</x:v>
       </x:c>
       <x:c r="F13" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Navigation</x:t>
         </x:is>
       </x:c>
       <x:c r="G13" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H13" s="10" t="str">
         <x:f>IF(A13="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A13," ","%20"))</x:f>
-        <x:v>Icone_ClickShare-1.svg</x:v>
+        <x:v>Navigation_Commande_Up.svg</x:v>
       </x:c>
       <x:c r="I13" s="8" t="inlineStr">
         <x:is>
@@ -822,7 +822,7 @@
     <x:row r="14" ht="34" customHeight="1">
       <x:c r="A14" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_ClickShare.svg</x:t>
+          <x:t xml:space="preserve">Video_Commande_Zoom+.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B14" s="8" t="inlineStr">
@@ -832,30 +832,30 @@
       </x:c>
       <x:c r="C14" s="9" t="str">
         <x:f>IF(A14="","",IFERROR(IF(VLOOKUP(B14,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B14,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D14" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone ClickShare</x:t>
+          <x:t xml:space="preserve">Zoom+</x:t>
         </x:is>
       </x:c>
       <x:c r="E14" s="9" t="str">
         <x:f>IF(A14="","",LOWER(B14&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A14),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_clickshare</x:v>
+        <x:v>lib001-video_commande_zoom+</x:v>
       </x:c>
       <x:c r="F14" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Sources vidéo</x:t>
         </x:is>
       </x:c>
       <x:c r="G14" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H14" s="10" t="str">
         <x:f>IF(A14="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A14," ","%20"))</x:f>
-        <x:v>Icone_ClickShare.svg</x:v>
+        <x:v>Video_Commande_Zoom%2B.svg</x:v>
       </x:c>
       <x:c r="I14" s="8" t="inlineStr">
         <x:is>
@@ -871,7 +871,7 @@
     <x:row r="15" ht="34" customHeight="1">
       <x:c r="A15" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_conseil.svg</x:t>
+          <x:t xml:space="preserve">Video_Commande_Zoom-_On.svg</x:t>
         </x:is>
       </x:c>
       <x:c r="B15" s="8" t="inlineStr">
@@ -881,30 +881,30 @@
       </x:c>
       <x:c r="C15" s="9" t="str">
         <x:f>IF(A15="","",IFERROR(IF(VLOOKUP(B15,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B15,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v>DGTS_DEFAUT</x:v>
       </x:c>
       <x:c r="D15" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone conseil</x:t>
+          <x:t xml:space="preserve">Zoom- On</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" s="9" t="str">
         <x:f>IF(A15="","",LOWER(B15&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A15),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_conseil</x:v>
+        <x:v>lib001-video_commande_zoom-_on</x:v>
       </x:c>
       <x:c r="F15" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve">Sources vidéo</x:t>
         </x:is>
       </x:c>
       <x:c r="G15" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve">Commande</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" s="10" t="str">
         <x:f>IF(A15="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A15," ","%20"))</x:f>
-        <x:v>Icone_conseil.svg</x:v>
+        <x:v>Video_Commande_Zoom-_On.svg</x:v>
       </x:c>
       <x:c r="I15" s="8" t="inlineStr">
         <x:is>
@@ -920,1176 +920,1176 @@
     <x:row r="16" ht="34" customHeight="1">
       <x:c r="A16" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_démo.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B16" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C16" s="9" t="str">
         <x:f>IF(A16="","",IFERROR(IF(VLOOKUP(B16,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B16,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D16" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone démo</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E16" s="9" t="str">
         <x:f>IF(A16="","",LOWER(B16&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A16),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_démo</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F16" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G16" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H16" s="10" t="str">
         <x:f>IF(A16="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A16," ","%20"))</x:f>
-        <x:v>Icone_d%C3%A9mo.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I16" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J16" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
       <x:c r="A17" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_formation.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B17" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C17" s="9" t="str">
         <x:f>IF(A17="","",IFERROR(IF(VLOOKUP(B17,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B17,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D17" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone formation</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E17" s="9" t="str">
         <x:f>IF(A17="","",LOWER(B17&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A17),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_formation</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F17" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G17" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H17" s="10" t="str">
         <x:f>IF(A17="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A17," ","%20"))</x:f>
-        <x:v>Icone_formation.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I17" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J17" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
       <x:c r="A18" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_pupitre.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B18" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C18" s="9" t="str">
         <x:f>IF(A18="","",IFERROR(IF(VLOOKUP(B18,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B18,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D18" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone pupitre</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E18" s="9" t="str">
         <x:f>IF(A18="","",LOWER(B18&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A18),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_pupitre</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F18" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G18" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H18" s="10" t="str">
         <x:f>IF(A18="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A18," ","%20"))</x:f>
-        <x:v>Icone_pupitre.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I18" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J18" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
       <x:c r="A19" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_USB-C-1.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B19" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C19" s="9" t="str">
         <x:f>IF(A19="","",IFERROR(IF(VLOOKUP(B19,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B19,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D19" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone USB-C-1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E19" s="9" t="str">
         <x:f>IF(A19="","",LOWER(B19&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A19),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_usb-c-1</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F19" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G19" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H19" s="10" t="str">
         <x:f>IF(A19="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A19," ","%20"))</x:f>
-        <x:v>Icone_USB-C-1.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I19" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J19" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
       <x:c r="A20" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone_USB-C.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B20" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C20" s="9" t="str">
         <x:f>IF(A20="","",IFERROR(IF(VLOOKUP(B20,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B20,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D20" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Icone USB-C</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E20" s="9" t="str">
         <x:f>IF(A20="","",LOWER(B20&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A20),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-icone_usb-c</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F20" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G20" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H20" s="10" t="str">
         <x:f>IF(A20="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A20," ","%20"))</x:f>
-        <x:v>Icone_USB-C.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I20" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J20" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
       <x:c r="A21" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo_Microsoft_Teams_(2025).svg 1.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B21" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C21" s="9" t="str">
         <x:f>IF(A21="","",IFERROR(IF(VLOOKUP(B21,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B21,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D21" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo Microsoft Teams (2025).svg 1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E21" s="9" t="str">
         <x:f>IF(A21="","",LOWER(B21&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A21),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-logo_microsoft_teams_(2025)-1</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F21" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G21" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H21" s="10" t="str">
         <x:f>IF(A21="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A21," ","%20"))</x:f>
-        <x:v>Logo_Microsoft_Teams_(2025).svg%201.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I21" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J21" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="22" ht="34" customHeight="1">
       <x:c r="A22" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe +-1.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B22" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C22" s="9" t="str">
         <x:f>IF(A22="","",IFERROR(IF(VLOOKUP(B22,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B22,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D22" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe +-1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E22" s="9" t="str">
         <x:f>IF(A22="","",LOWER(B22&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A22),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-loupe-+-1</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F22" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G22" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H22" s="10" t="str">
         <x:f>IF(A22="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A22," ","%20"))</x:f>
-        <x:v>Loupe%20%2B-1.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I22" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J22" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
       <x:c r="A23" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe +.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B23" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C23" s="9" t="str">
         <x:f>IF(A23="","",IFERROR(IF(VLOOKUP(B23,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B23,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D23" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe +</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E23" s="9" t="str">
         <x:f>IF(A23="","",LOWER(B23&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A23),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-loupe-+</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F23" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G23" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H23" s="10" t="str">
         <x:f>IF(A23="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A23," ","%20"))</x:f>
-        <x:v>Loupe%20%2B.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I23" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J23" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
       <x:c r="A24" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe --1.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B24" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C24" s="9" t="str">
         <x:f>IF(A24="","",IFERROR(IF(VLOOKUP(B24,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B24,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D24" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe --1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E24" s="9" t="str">
         <x:f>IF(A24="","",LOWER(B24&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A24),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-loupe---1</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F24" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G24" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H24" s="10" t="str">
         <x:f>IF(A24="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A24," ","%20"))</x:f>
-        <x:v>Loupe%20--1.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I24" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J24" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
       <x:c r="A25" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe -.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B25" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C25" s="9" t="str">
         <x:f>IF(A25="","",IFERROR(IF(VLOOKUP(B25,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B25,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D25" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Loupe -</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E25" s="9" t="str">
         <x:f>IF(A25="","",LOWER(B25&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A25),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-loupe--</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F25" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G25" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H25" s="10" t="str">
         <x:f>IF(A25="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A25," ","%20"))</x:f>
-        <x:v>Loupe%20-.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I25" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J25" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
       <x:c r="A26" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Retour-1.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B26" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C26" s="9" t="str">
         <x:f>IF(A26="","",IFERROR(IF(VLOOKUP(B26,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B26,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D26" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Retour-1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E26" s="9" t="str">
         <x:f>IF(A26="","",LOWER(B26&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A26),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-retour-1</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F26" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G26" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H26" s="10" t="str">
         <x:f>IF(A26="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A26," ","%20"))</x:f>
-        <x:v>Retour-1.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I26" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J26" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
       <x:c r="A27" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Retour.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B27" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C27" s="9" t="str">
         <x:f>IF(A27="","",IFERROR(IF(VLOOKUP(B27,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B27,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D27" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Retour</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E27" s="9" t="str">
         <x:f>IF(A27="","",LOWER(B27&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A27),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-retour</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F27" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G27" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H27" s="10" t="str">
         <x:f>IF(A27="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A27," ","%20"))</x:f>
-        <x:v>Retour.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I27" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J27" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
       <x:c r="A28" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-1.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B28" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C28" s="9" t="str">
         <x:f>IF(A28="","",IFERROR(IF(VLOOKUP(B28,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B28,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D28" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E28" s="9" t="str">
         <x:f>IF(A28="","",LOWER(B28&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A28),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-1</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F28" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G28" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H28" s="10" t="str">
         <x:f>IF(A28="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A28," ","%20"))</x:f>
-        <x:v>Vector-1.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I28" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J28" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="29" ht="34" customHeight="1">
       <x:c r="A29" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-10.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B29" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C29" s="9" t="str">
         <x:f>IF(A29="","",IFERROR(IF(VLOOKUP(B29,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B29,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D29" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-10</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E29" s="9" t="str">
         <x:f>IF(A29="","",LOWER(B29&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A29),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-10</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F29" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G29" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H29" s="10" t="str">
         <x:f>IF(A29="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A29," ","%20"))</x:f>
-        <x:v>Vector-10.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I29" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J29" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="30" ht="34" customHeight="1">
       <x:c r="A30" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-11.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B30" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C30" s="9" t="str">
         <x:f>IF(A30="","",IFERROR(IF(VLOOKUP(B30,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B30,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D30" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-11</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E30" s="9" t="str">
         <x:f>IF(A30="","",LOWER(B30&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A30),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-11</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F30" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G30" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H30" s="10" t="str">
         <x:f>IF(A30="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A30," ","%20"))</x:f>
-        <x:v>Vector-11.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I30" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J30" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="31" ht="34" customHeight="1">
       <x:c r="A31" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-2.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B31" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C31" s="9" t="str">
         <x:f>IF(A31="","",IFERROR(IF(VLOOKUP(B31,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B31,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D31" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E31" s="9" t="str">
         <x:f>IF(A31="","",LOWER(B31&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A31),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-2</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F31" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G31" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H31" s="10" t="str">
         <x:f>IF(A31="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A31," ","%20"))</x:f>
-        <x:v>Vector-2.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I31" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J31" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="32" ht="34" customHeight="1">
       <x:c r="A32" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-3.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B32" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C32" s="9" t="str">
         <x:f>IF(A32="","",IFERROR(IF(VLOOKUP(B32,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B32,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D32" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-3</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E32" s="9" t="str">
         <x:f>IF(A32="","",LOWER(B32&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A32),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-3</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F32" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G32" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H32" s="10" t="str">
         <x:f>IF(A32="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A32," ","%20"))</x:f>
-        <x:v>Vector-3.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I32" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J32" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
       <x:c r="A33" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-4.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B33" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C33" s="9" t="str">
         <x:f>IF(A33="","",IFERROR(IF(VLOOKUP(B33,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B33,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D33" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-4</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E33" s="9" t="str">
         <x:f>IF(A33="","",LOWER(B33&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A33),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-4</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F33" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G33" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H33" s="10" t="str">
         <x:f>IF(A33="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A33," ","%20"))</x:f>
-        <x:v>Vector-4.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I33" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J33" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
       <x:c r="A34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-5.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C34" s="9" t="str">
         <x:f>IF(A34="","",IFERROR(IF(VLOOKUP(B34,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B34,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E34" s="9" t="str">
         <x:f>IF(A34="","",LOWER(B34&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A34),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-5</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H34" s="10" t="str">
         <x:f>IF(A34="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A34," ","%20"))</x:f>
-        <x:v>Vector-5.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="35" ht="34" customHeight="1">
       <x:c r="A35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-6.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C35" s="9" t="str">
         <x:f>IF(A35="","",IFERROR(IF(VLOOKUP(B35,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B35,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E35" s="9" t="str">
         <x:f>IF(A35="","",LOWER(B35&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A35),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-6</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H35" s="10" t="str">
         <x:f>IF(A35="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A35," ","%20"))</x:f>
-        <x:v>Vector-6.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
       <x:c r="A36" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-7.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B36" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C36" s="9" t="str">
         <x:f>IF(A36="","",IFERROR(IF(VLOOKUP(B36,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B36,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D36" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E36" s="9" t="str">
         <x:f>IF(A36="","",LOWER(B36&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A36),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-7</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F36" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G36" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H36" s="10" t="str">
         <x:f>IF(A36="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A36," ","%20"))</x:f>
-        <x:v>Vector-7.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I36" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J36" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37" ht="34" customHeight="1">
       <x:c r="A37" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-8.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B37" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C37" s="9" t="str">
         <x:f>IF(A37="","",IFERROR(IF(VLOOKUP(B37,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B37,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D37" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-8</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E37" s="9" t="str">
         <x:f>IF(A37="","",LOWER(B37&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A37),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-8</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F37" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G37" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H37" s="10" t="str">
         <x:f>IF(A37="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A37," ","%20"))</x:f>
-        <x:v>Vector-8.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I37" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J37" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38" ht="34" customHeight="1">
       <x:c r="A38" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-9.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B38" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C38" s="9" t="str">
         <x:f>IF(A38="","",IFERROR(IF(VLOOKUP(B38,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B38,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D38" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector-9</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E38" s="9" t="str">
         <x:f>IF(A38="","",LOWER(B38&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A38),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector-9</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F38" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G38" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H38" s="10" t="str">
         <x:f>IF(A38="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A38," ","%20"))</x:f>
-        <x:v>Vector-9.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I38" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J38" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
       <x:c r="A39" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector.svg</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="B39" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">lib001</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="C39" s="9" t="str">
         <x:f>IF(A39="","",IFERROR(IF(VLOOKUP(B39,Bibliotheques!$A$10:$B$59,2,FALSE)=0,"Nom manquant",VLOOKUP(B39,Bibliotheques!$A$10:$B$59,2,FALSE)),"Clé inconnue"))</x:f>
-        <x:v>DGTS</x:v>
+        <x:v/>
       </x:c>
       <x:c r="D39" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Vector</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E39" s="9" t="str">
         <x:f>IF(A39="","",LOWER(B39&amp;"-"&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(A39),".svg","")," ","-"),"/","-")))</x:f>
-        <x:v>lib001-vector</x:v>
+        <x:v/>
       </x:c>
       <x:c r="F39" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Custom</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="G39" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Non classées</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H39" s="10" t="str">
         <x:f>IF(A39="","",IF(Bibliotheques!$B$5="","",Bibliotheques!$B$5&amp;IF(RIGHT(Bibliotheques!$B$5,1)="/","","/"))&amp;SUBSTITUTE(A39," ","%20"))</x:f>
-        <x:v>Vector.svg</x:v>
+        <x:v/>
       </x:c>
       <x:c r="I39" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Oui</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="J39" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">icon</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
     </x:row>
@@ -49568,7 +49568,7 @@
       </x:c>
       <x:c r="B10" s="8" t="inlineStr">
         <x:is>
-          <x:t>DGTS</x:t>
+          <x:t>DGTS_DEFAUT</x:t>
         </x:is>
       </x:c>
       <x:c r="C10" s="1"/>
